--- a/packages/server/src/models/training_data.xlsx
+++ b/packages/server/src/models/training_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\websites\Personal Financial Assistance\PersonalFinancialAssistance\packages\server\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\websites\Personal Financial Assistance\PersonalFinancialAssistance\packages\server\src\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9724636D-C53E-4321-B23B-64DBCA9FB385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2101A4F0-5122-41B3-8F28-6CD22EA061E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9690" yWindow="585" windowWidth="9660" windowHeight="8865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3002" uniqueCount="944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="951">
   <si>
     <t>description</t>
   </si>
@@ -2852,6 +2852,27 @@
   </si>
   <si>
     <t>METRO # #9384 TORONTO</t>
+  </si>
+  <si>
+    <t>PROV/LOCAL GVT PAYMENT</t>
+  </si>
+  <si>
+    <t>ONLINE BANKING TRANSFER</t>
+  </si>
+  <si>
+    <t>Transfers &amp; Cash</t>
+  </si>
+  <si>
+    <t>ATM Deposit</t>
+  </si>
+  <si>
+    <t>MISC PAYMENT</t>
+  </si>
+  <si>
+    <t>E-TRANSFER SENT</t>
+  </si>
+  <si>
+    <t>E-TRANSFER - AUTODEPOSIT</t>
   </si>
 </sst>
 </file>
@@ -3191,7 +3212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1501"/>
+  <dimension ref="A1:B1507"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -15206,6 +15227,54 @@
         <v>15</v>
       </c>
     </row>
+    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1502" t="s">
+        <v>944</v>
+      </c>
+      <c r="B1502" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1503" t="s">
+        <v>945</v>
+      </c>
+      <c r="B1503" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1504" t="s">
+        <v>947</v>
+      </c>
+      <c r="B1504" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1505" t="s">
+        <v>948</v>
+      </c>
+      <c r="B1505" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1506" t="s">
+        <v>949</v>
+      </c>
+      <c r="B1506" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1507" t="s">
+        <v>950</v>
+      </c>
+      <c r="B1507" t="s">
+        <v>946</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
